--- a/attendance/attendance.xlsx
+++ b/attendance/attendance.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -46,8 +49,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,133 +419,60 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>College ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>College</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>04-10-2026</t>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Section</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>k26047</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Aaditya Sharma</t>
+          <t>Ayush suwalka</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Aayush Suwalka</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>PRESENT</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Bharat Goswami</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>PRESENT</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Pranav Sharma</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Pulkit Sharma</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>PRESENT</t>
+          <t>AI/ML</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>3rd Year</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>

--- a/attendance/attendance.xlsx
+++ b/attendance/attendance.xlsx
@@ -419,8 +419,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -435,17 +443,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Branch</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Section</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -462,17 +475,54 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>3rd Year</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>AI/ML</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>3rd Year</t>
-        </is>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>k27934</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1st Year</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>dss</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
         </is>
       </c>
     </row>
